--- a/AfterToken/Configs/GameConfig/Datas/camera3d.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/camera3d.xlsx
@@ -625,10 +625,10 @@
         <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>-10</v>
+        <v>-3.5</v>
       </c>
       <c r="F4" t="n">
         <v>45</v>
